--- a/template.xlsx
+++ b/template.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveuclac-my.sharepoint.com/personal/zcftfg3_ucl_ac_uk/Documents/MADE/TEST-B-made/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekm1/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{5E6D5B80-E360-CD42-B984-476B2537B989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{653BB7A9-CEC5-6541-9566-3C12CD07912C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BD42911-05F1-DB49-9B5E-223FDF259688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="3040" windowWidth="29340" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="860" yWindow="1760" windowWidth="34740" windowHeight="19680" xr2:uid="{63139DA3-2AAE-014D-AF2B-8E259CF4D64C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Programme-Name" sheetId="1" r:id="rId1"/>
+    <sheet name="MSci" sheetId="1" r:id="rId1"/>
+    <sheet name="KEYS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
   <si>
     <t>Module</t>
   </si>
@@ -47,90 +48,154 @@
     <t>Task</t>
   </si>
   <si>
-    <t>1-10</t>
-  </si>
-  <si>
-    <t>10-20</t>
-  </si>
-  <si>
-    <t>21+</t>
-  </si>
-  <si>
-    <t>Likelihood of B-made input expected</t>
-  </si>
-  <si>
-    <t>Activity start</t>
-  </si>
-  <si>
-    <t>Activity end</t>
+    <t>Likelihood of B-made Input Expected</t>
+  </si>
+  <si>
+    <t>Overall Cohort Size</t>
+  </si>
+  <si>
+    <t>Percentage of Students Expected</t>
+  </si>
+  <si>
+    <t>Student # Expected</t>
+  </si>
+  <si>
+    <t>Activity Start</t>
+  </si>
+  <si>
+    <t>Activity End</t>
+  </si>
+  <si>
+    <t>Tentative or Known?</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>e.g. Module 1</t>
-  </si>
-  <si>
-    <t>e.g. Module 2</t>
-  </si>
-  <si>
-    <t>e.g. Module 3</t>
-  </si>
-  <si>
-    <t>e.g. 1</t>
-  </si>
-  <si>
-    <t>e.g. 2</t>
-  </si>
-  <si>
-    <t>e.g. 3</t>
-  </si>
-  <si>
-    <t>e.g. Deadline</t>
-  </si>
-  <si>
-    <t>e.g. Crit</t>
-  </si>
-  <si>
-    <t>e.g. Planned Teaching</t>
-  </si>
-  <si>
-    <t>e.g. Gordon Street</t>
-  </si>
-  <si>
-    <t>e.g. Here East</t>
-  </si>
-  <si>
-    <t>e.g. Wicklow Street</t>
-  </si>
-  <si>
-    <t>KEY</t>
-  </si>
-  <si>
-    <t>Level of B-made input expected (number of students)</t>
-  </si>
-  <si>
-    <t>Definite</t>
-  </si>
-  <si>
-    <t>Likely</t>
-  </si>
-  <si>
-    <t>Possible</t>
+    <t>Keywords</t>
+  </si>
+  <si>
+    <t>code or descriptor</t>
+  </si>
+  <si>
+    <t>per year group</t>
+  </si>
+  <si>
+    <t>choose from list</t>
+  </si>
+  <si>
+    <t>choose from list:
+0 - none
+1 - possible
+2 - likely
+3 - definite</t>
+  </si>
+  <si>
+    <t>students in whole group</t>
+  </si>
+  <si>
+    <t>% expected to attend</t>
+  </si>
+  <si>
+    <t>calculated</t>
+  </si>
+  <si>
+    <t>for planned teaching, e.g. casting, robotics, welding, 3D printing</t>
+  </si>
+  <si>
+    <t>Planned Teaching</t>
+  </si>
+  <si>
+    <t>Known</t>
+  </si>
+  <si>
+    <t>Gordon Street</t>
+  </si>
+  <si>
+    <t>Deadline</t>
+  </si>
+  <si>
+    <t>General / Coursework</t>
+  </si>
+  <si>
+    <t>Tentative</t>
+  </si>
+  <si>
+    <t>Field Trip</t>
+  </si>
+  <si>
+    <t>Crit</t>
+  </si>
+  <si>
+    <t>Here East</t>
+  </si>
+  <si>
+    <t>Exhibition Build</t>
+  </si>
+  <si>
+    <t>Off Site</t>
+  </si>
+  <si>
+    <t>Induction</t>
+  </si>
+  <si>
+    <t>Wicklow Street</t>
+  </si>
+  <si>
+    <t>Marshgate</t>
+  </si>
+  <si>
+    <t>BARC0140 - Making Architecture</t>
+  </si>
+  <si>
+    <t>BARC0146 - Skills Portfolio</t>
+  </si>
+  <si>
+    <t>BARC0142 - 	Sample Building</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARC0145 - 	History and Theory </t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Module Duration</t>
+  </si>
+  <si>
+    <t>EC?</t>
+  </si>
+  <si>
+    <t>BARC0144 - Environmental Concepts and Tools</t>
+  </si>
+  <si>
+    <t>BARC0143 - Structural Concepts and Tools</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="1"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -140,13 +205,28 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="1"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,42 +240,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00C875"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDAB3D"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF2F4A"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF007EB5"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9D50DD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF037F4C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -204,92 +278,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color rgb="FF00B461"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="thick">
-        <color rgb="FF00B461"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="thick">
-        <color rgb="FF00B461"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="thick">
-        <color rgb="FF00B461"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFE99729"/>
-      </left>
-      <right style="thick">
-        <color rgb="FFE99729"/>
-      </right>
-      <top style="thick">
-        <color rgb="FFE99729"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FFE99729"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFCE3048"/>
-      </left>
-      <right style="thick">
-        <color rgb="FFCE3048"/>
-      </right>
-      <top style="thick">
-        <color rgb="FFCE3048"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FFCE3048"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF3DB0DF"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF3DB0DF"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF3DB0DF"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF3DB0DF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF9238AF"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF9238AF"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF9238AF"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF9238AF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF006B38"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF006B38"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF006B38"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF006B38"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -297,66 +296,117 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -684,198 +734,1358 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58F9EFE7-CD97-734A-9069-6AA6DD88B87D}">
+  <dimension ref="A1:M75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="16" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" style="18"/>
+    <col min="1" max="1" width="46.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="10" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="32.33203125" style="7" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="7" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="15" customFormat="1" ht="71" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:13" ht="60" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="82" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="6">
+        <v>3</v>
+      </c>
+      <c r="E3" s="7">
+        <v>60</v>
+      </c>
+      <c r="F3" s="7">
+        <v>100</v>
+      </c>
+      <c r="G3" s="6">
+        <f t="shared" ref="G3:G54" si="0">ROUNDUP(E3*F3%, 0)</f>
+        <v>60</v>
+      </c>
+      <c r="H3" s="16">
+        <v>46293</v>
+      </c>
+      <c r="I3" s="16">
+        <v>46293</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="6">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7">
+        <v>60</v>
+      </c>
+      <c r="F4" s="7">
+        <v>50</v>
+      </c>
+      <c r="G4" s="6">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H4" s="16">
+        <v>46342</v>
+      </c>
+      <c r="I4" s="16">
+        <v>46342</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="16"/>
-      <c r="K1" s="14" t="s">
+      <c r="D5" s="6">
+        <v>2</v>
+      </c>
+      <c r="E5" s="7">
+        <v>60</v>
+      </c>
+      <c r="F5" s="7">
+        <v>50</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H5" s="17">
+        <v>46366</v>
+      </c>
+      <c r="I5" s="17">
+        <v>46366</v>
+      </c>
+      <c r="J5" s="25">
+        <f>I5+14</f>
+        <v>46380</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="6" customFormat="1" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>60</v>
+      </c>
+      <c r="F6" s="7">
+        <v>100</v>
+      </c>
+      <c r="G6" s="6">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="H6" s="17">
+        <v>46405</v>
+      </c>
+      <c r="I6" s="17">
+        <v>46407</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7">
+        <v>60</v>
+      </c>
+      <c r="F7" s="7">
+        <v>30</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="H7" s="17">
+        <v>46426</v>
+      </c>
+      <c r="I7" s="17">
+        <v>46426</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="4">
+        <v>3</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="6">
+        <v>2</v>
+      </c>
+      <c r="E8" s="7">
+        <v>60</v>
+      </c>
+      <c r="F8" s="7">
+        <v>30</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" ref="G8" si="1">ROUNDUP(E8*F8%, 0)</f>
+        <v>18</v>
+      </c>
+      <c r="H8" s="17">
+        <v>46426</v>
+      </c>
+      <c r="I8" s="17">
+        <v>46426</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="4">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="6">
+        <v>2</v>
+      </c>
+      <c r="E9" s="7">
+        <v>30</v>
+      </c>
+      <c r="F9" s="7">
+        <v>40</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="H9" s="17">
+        <v>46463</v>
+      </c>
+      <c r="I9" s="17">
+        <v>46463</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="18">
+        <v>1</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="19">
+        <v>2</v>
+      </c>
+      <c r="E10" s="18">
+        <v>60</v>
+      </c>
+      <c r="F10" s="18">
+        <v>30</v>
+      </c>
+      <c r="G10" s="19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="H10" s="20">
+        <v>46293</v>
+      </c>
+      <c r="I10" s="20">
+        <v>46527</v>
+      </c>
+      <c r="J10" s="21"/>
+      <c r="K10" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="18">
+        <v>1</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="19">
+        <v>2</v>
+      </c>
+      <c r="E11" s="18">
+        <v>60</v>
+      </c>
+      <c r="F11" s="18">
+        <v>30</v>
+      </c>
+      <c r="G11" s="19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="H11" s="24">
+        <v>46295</v>
+      </c>
+      <c r="I11" s="24">
+        <v>46374</v>
+      </c>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="18">
+        <v>2</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="19">
+        <v>2</v>
+      </c>
+      <c r="E12" s="18">
+        <v>60</v>
+      </c>
+      <c r="F12" s="18">
+        <v>30</v>
+      </c>
+      <c r="G12" s="19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="H12" s="20">
+        <v>46349</v>
+      </c>
+      <c r="I12" s="20">
+        <v>46527</v>
+      </c>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="18">
+        <v>2</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="19">
+        <v>2</v>
+      </c>
+      <c r="E13" s="18">
+        <v>60</v>
+      </c>
+      <c r="F13" s="18">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="10">
+      <c r="G13" s="19">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H13" s="20">
+        <v>46297</v>
+      </c>
+      <c r="I13" s="20">
+        <v>46451</v>
+      </c>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="18">
+        <v>3</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="19">
         <v>1</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E14" s="18">
+        <v>60</v>
+      </c>
+      <c r="F14" s="18">
+        <v>5</v>
+      </c>
+      <c r="G14" s="19">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F2" s="2">
-        <v>46034</v>
-      </c>
-      <c r="G2" s="2">
-        <v>46036</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="17"/>
-      <c r="K2" s="10">
+      <c r="H14" s="20">
+        <v>46297</v>
+      </c>
+      <c r="I14" s="20">
+        <v>46451</v>
+      </c>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="18">
+        <v>3</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="19">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="E15" s="18">
+        <v>60</v>
+      </c>
+      <c r="F15" s="18">
+        <v>5</v>
+      </c>
+      <c r="G15" s="19">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H15" s="20">
+        <v>46400</v>
+      </c>
+      <c r="I15" s="20">
+        <v>46506</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="31"/>
+    </row>
+    <row r="17" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="31"/>
+    </row>
+    <row r="18" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="31"/>
+    </row>
+    <row r="19" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="31"/>
+    </row>
+    <row r="20" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="31"/>
+    </row>
+    <row r="21" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="31"/>
+    </row>
+    <row r="22" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="31"/>
+    </row>
+    <row r="23" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="36"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="31"/>
+    </row>
+    <row r="24" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="31"/>
+    </row>
+    <row r="25" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="31"/>
+    </row>
+    <row r="26" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="31"/>
+    </row>
+    <row r="27" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="31"/>
+    </row>
+    <row r="28" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="31"/>
+    </row>
+    <row r="29" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="31"/>
+    </row>
+    <row r="30" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="31"/>
+    </row>
+    <row r="31" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="31"/>
+    </row>
+    <row r="32" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="31"/>
+    </row>
+    <row r="33" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="36"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="31"/>
+    </row>
+    <row r="34" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="36"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="31"/>
+    </row>
+    <row r="35" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="31"/>
+    </row>
+    <row r="36" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="36"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="31"/>
+    </row>
+    <row r="37" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="36"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="34"/>
+      <c r="L37" s="31"/>
+    </row>
+    <row r="38" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="36"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="34"/>
+      <c r="L38" s="31"/>
+    </row>
+    <row r="39" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="34"/>
+      <c r="L39" s="31"/>
+    </row>
+    <row r="40" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="34"/>
+      <c r="L40" s="31"/>
+    </row>
+    <row r="41" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="34"/>
+      <c r="L41" s="31"/>
+    </row>
+    <row r="42" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="34"/>
+      <c r="L42" s="31"/>
+    </row>
+    <row r="43" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="31"/>
+    </row>
+    <row r="44" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="34"/>
+      <c r="L44" s="31"/>
+    </row>
+    <row r="45" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="34"/>
+      <c r="L45" s="31"/>
+    </row>
+    <row r="46" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="34"/>
+      <c r="L46" s="31"/>
+    </row>
+    <row r="47" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="31"/>
+    </row>
+    <row r="48" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="37"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="34"/>
+      <c r="L48" s="31"/>
+    </row>
+    <row r="49" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="37"/>
+      <c r="I49" s="37"/>
+      <c r="J49" s="35"/>
+      <c r="K49" s="34"/>
+      <c r="L49" s="31"/>
+    </row>
+    <row r="50" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="34"/>
+      <c r="L50" s="31"/>
+    </row>
+    <row r="51" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="36"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="31"/>
+    </row>
+    <row r="52" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="37"/>
+      <c r="I52" s="37"/>
+      <c r="J52" s="33"/>
+      <c r="K52" s="34"/>
+      <c r="L52" s="31"/>
+    </row>
+    <row r="53" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="36"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="33"/>
+      <c r="K53" s="34"/>
+      <c r="L53" s="31"/>
+    </row>
+    <row r="54" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="36"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="34"/>
+      <c r="L54" s="31"/>
+    </row>
+    <row r="55" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="33"/>
+      <c r="K55" s="34"/>
+      <c r="L55" s="31"/>
+    </row>
+    <row r="56" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C56" s="31"/>
+      <c r="D56" s="31"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="33"/>
+      <c r="K56" s="34"/>
+      <c r="L56" s="31"/>
+    </row>
+    <row r="57" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C57" s="31"/>
+      <c r="D57" s="31"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="34"/>
+      <c r="L57" s="31"/>
+    </row>
+    <row r="58" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="33"/>
+      <c r="K58" s="34"/>
+      <c r="L58" s="31"/>
+    </row>
+    <row r="59" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="37"/>
+      <c r="I59" s="37"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="34"/>
+      <c r="L59" s="31"/>
+    </row>
+    <row r="60" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="G60" s="31"/>
+      <c r="H60" s="37"/>
+      <c r="I60" s="37"/>
+      <c r="J60" s="35"/>
+      <c r="K60" s="34"/>
+      <c r="L60" s="31"/>
+    </row>
+    <row r="61" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="33"/>
+      <c r="K61" s="34"/>
+      <c r="L61" s="31"/>
+    </row>
+    <row r="62" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C62" s="31"/>
+      <c r="D62" s="31"/>
+      <c r="G62" s="31"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="33"/>
+      <c r="K62" s="34"/>
+      <c r="L62" s="31"/>
+    </row>
+    <row r="63" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C63" s="31"/>
+      <c r="D63" s="31"/>
+      <c r="G63" s="31"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="34"/>
+      <c r="L63" s="31"/>
+    </row>
+    <row r="64" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="35"/>
+      <c r="K64" s="34"/>
+      <c r="L64" s="31"/>
+    </row>
+    <row r="65" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
+      <c r="G65" s="31"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+      <c r="J65" s="33"/>
+      <c r="K65" s="34"/>
+      <c r="L65" s="31"/>
+    </row>
+    <row r="66" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C66" s="31"/>
+      <c r="D66" s="31"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="37"/>
+      <c r="I66" s="37"/>
+      <c r="J66" s="35"/>
+      <c r="K66" s="34"/>
+      <c r="L66" s="31"/>
+    </row>
+    <row r="67" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="37"/>
+      <c r="I67" s="37"/>
+      <c r="J67" s="35"/>
+      <c r="K67" s="34"/>
+      <c r="L67" s="31"/>
+    </row>
+    <row r="68" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C68" s="31"/>
+      <c r="D68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
+      <c r="J68" s="33"/>
+      <c r="K68" s="34"/>
+      <c r="L68" s="31"/>
+    </row>
+    <row r="69" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
+      <c r="J69" s="33"/>
+      <c r="K69" s="34"/>
+      <c r="L69" s="31"/>
+    </row>
+    <row r="70" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="33"/>
+      <c r="K70" s="34"/>
+      <c r="L70" s="31"/>
+    </row>
+    <row r="71" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C71" s="31"/>
+      <c r="D71" s="31"/>
+      <c r="G71" s="31"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="33"/>
+      <c r="K71" s="34"/>
+      <c r="L71" s="31"/>
+    </row>
+    <row r="72" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="33"/>
+      <c r="K72" s="34"/>
+      <c r="L72" s="31"/>
+    </row>
+    <row r="73" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C73" s="31"/>
+      <c r="D73" s="31"/>
+      <c r="G73" s="31"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="32"/>
+      <c r="J73" s="33"/>
+      <c r="K73" s="34"/>
+      <c r="L73" s="31"/>
+    </row>
+    <row r="74" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C74" s="31"/>
+      <c r="D74" s="31"/>
+      <c r="G74" s="31"/>
+      <c r="H74" s="32"/>
+      <c r="I74" s="32"/>
+      <c r="J74" s="33"/>
+      <c r="K74" s="34"/>
+      <c r="L74" s="31"/>
+    </row>
+    <row r="75" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
+      <c r="J75" s="33"/>
+      <c r="K75" s="34"/>
+      <c r="L75" s="31"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{885F5CA5-1EC0-824F-B71B-1C02EEA82470}">
+          <x14:formula1>
+            <xm:f>KEYS!$B$17:$B$20</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D75</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3658271E-3007-7F44-9A4A-CA8870E89425}">
+          <x14:formula1>
+            <xm:f>KEYS!$B$22:$B$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>K3:K75</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{848E1D04-BE49-A941-92BD-B47CD6F5AC00}">
+          <x14:formula1>
+            <xm:f>KEYS!$B$2:$B$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>C3:C75</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7049AEC8-2D38-EB44-AD0B-D5E41FF5E481}">
+          <x14:formula1>
+            <xm:f>KEYS!$B$11:$B$15</xm:f>
+          </x14:formula1>
+          <xm:sqref>L3:L75</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B1D51D-2243-4249-825C-F16A725FFAE5}">
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" style="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B2" s="27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B3" s="27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B4" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="6" customFormat="1" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="11">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B5" s="26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B6" s="26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B7" s="26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B8" s="26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B9" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B11" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B12" s="26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B13" s="26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B14" s="26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B15" s="26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B19" s="14">
         <v>2</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2">
-        <v>46044</v>
-      </c>
-      <c r="G3" s="2">
-        <v>46049</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="K3" s="11">
-        <v>2</v>
-      </c>
-      <c r="L3" s="6" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B22" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="6" customFormat="1" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="12">
-        <v>3</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2">
-        <v>46048</v>
-      </c>
-      <c r="G4" s="2">
-        <v>46059</v>
-      </c>
-      <c r="H4" s="2" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B23" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="17"/>
-      <c r="K4" s="12">
-        <v>3</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A7" s="1"/>
-      <c r="B7" s="3"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A8" s="1"/>
-      <c r="B8" s="3"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A9" s="1"/>
-      <c r="B9" s="3"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="F12" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{1faf88fe-a998-4c5b-93c9-210a11d9a5c2}" enabled="0" method="" siteId="{1faf88fe-a998-4c5b-93c9-210a11d9a5c2}" removed="1"/>
+</clbl:labelList>
 </file>